--- a/hosp3down.xlsx
+++ b/hosp3down.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,67 +367,47 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>PLT</t>
+          <t>cluster</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>CSP diff%</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>cluster</t>
+          <t>addr</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CSP diff%</t>
+          <t>city</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>addr</t>
+          <t>state</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>contact</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>phone</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>zip</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>lat</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>lon</t>
         </is>
       </c>
     </row>
@@ -442,55 +422,43 @@
           <t>CANTON POTSDAM HOSPITAL</t>
         </is>
       </c>
-      <c r="C2">
-        <v>18.4204271640893</v>
-      </c>
-      <c r="D2">
-        <v>69.9166666666666</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-31.7554912310573</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G2">
-        <v>-31.7554912310573</v>
+          <t>50 LEROY STREET</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>POTSDAM</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50 LEROY STREET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>POTSDAM</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+          <t>13676</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>315-265-3300</t>
         </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>13676</t>
-        </is>
-      </c>
-      <c r="N2">
-        <v>44.676131</v>
-      </c>
-      <c r="O2">
-        <v>-74.98148</v>
       </c>
     </row>
     <row r="3">
@@ -504,60 +472,48 @@
           <t>NORTHEAST GEORGIA MEDICAL CTR-BRASELTON</t>
         </is>
       </c>
-      <c r="C3">
-        <v>19.0809336149515</v>
-      </c>
-      <c r="D3">
-        <v>69.23684210526309</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>-38.4720638540478</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G3">
-        <v>-38.4720638540478</v>
+          <t>1400 RIVER PLACE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BRASELTON</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1400 RIVER PLACE</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BRASELTON</t>
+          <t>30517</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>770-219-9000</t>
         </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>30517</t>
-        </is>
-      </c>
-      <c r="N3">
-        <v>34.120226</v>
-      </c>
-      <c r="O3">
-        <v>-83.83741999999999</v>
       </c>
     </row>
     <row r="4">
@@ -571,60 +527,48 @@
           <t>PHOEBE PUTNEY MEMORIAL HOSP</t>
         </is>
       </c>
-      <c r="C4">
-        <v>5.43679879643533</v>
-      </c>
-      <c r="D4">
-        <v>236.113636363636</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>-25.3890332723714</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-25.3890332723714</v>
+          <t>417 THIRD AVENUE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ALBANY</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>417 THIRD AVENUE</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ALBANY</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>DIAN SWAFFORD</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>DIAN SWAFFORD</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
           <t>229-312-6120</t>
         </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>31701</t>
-        </is>
-      </c>
-      <c r="N4">
-        <v>31.590209</v>
-      </c>
-      <c r="O4">
-        <v>-84.15734999999999</v>
       </c>
     </row>
     <row r="5">
@@ -638,50 +582,38 @@
           <t>FRYE REGIONAL HOSPITAL</t>
         </is>
       </c>
-      <c r="C5">
-        <v>15.7998141864975</v>
-      </c>
-      <c r="D5">
-        <v>65.04878048780481</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>-23.9886680831562</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>-23.9886680831562</v>
+          <t>420 N. CENTER STREET</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HICKORY</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>420 N. CENTER STREET</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HICKORY</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>28601</t>
         </is>
-      </c>
-      <c r="N5">
-        <v>35.737679</v>
-      </c>
-      <c r="O5">
-        <v>-81.33756</v>
       </c>
     </row>
     <row r="6">
@@ -695,55 +627,43 @@
           <t>HURLEY MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C6">
-        <v>9.192775014397579</v>
-      </c>
-      <c r="D6">
-        <v>110.81081081081</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>-20.8630393996247</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>-20.8630393996247</v>
+          <t>1 HURLEY PLAZA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FLINT</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1 HURLEY PLAZA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FLINT</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+          <t>48503</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>810-262-9000</t>
         </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>48503</t>
-        </is>
-      </c>
-      <c r="N6">
-        <v>43.021845</v>
-      </c>
-      <c r="O6">
-        <v>-83.70496</v>
       </c>
     </row>
     <row r="7">
@@ -757,55 +677,43 @@
           <t>MCLAREN NORTHERN MICHIGAN</t>
         </is>
       </c>
-      <c r="C7">
-        <v>16.0352390329662</v>
-      </c>
-      <c r="D7">
-        <v>116.757575757575</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>-14.9570235568922</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>-14.9570235568922</v>
+          <t>416 CONNABLE AVE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PETOSKEY</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>416 CONNABLE AVE</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PETOSKEY</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+          <t>49770</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>231-487-4165</t>
         </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>49770</t>
-        </is>
-      </c>
-      <c r="N7">
-        <v>45.373466</v>
-      </c>
-      <c r="O7">
-        <v>-84.96912</v>
       </c>
     </row>
     <row r="8">
@@ -819,55 +727,43 @@
           <t>LOURDES HOSPITAL</t>
         </is>
       </c>
-      <c r="C8">
-        <v>6.73825241497309</v>
-      </c>
-      <c r="D8">
-        <v>174.75</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>-35.9084406294706</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G8">
-        <v>-35.9084406294706</v>
+          <t>1530 LONE OAK RD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PADUCAH</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1530 LONE OAK RD</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PADUCAH</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+          <t>42003</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>270-444-2142</t>
         </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>42003</t>
-        </is>
-      </c>
-      <c r="N8">
-        <v>37.052986</v>
-      </c>
-      <c r="O8">
-        <v>-88.64784</v>
       </c>
     </row>
     <row r="9">
@@ -881,60 +777,48 @@
           <t>KADLEC REGIONAL MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C9">
-        <v>4.47197355856456</v>
-      </c>
-      <c r="D9">
-        <v>232.923076923076</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>-16.8668187822745</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G9">
-        <v>-16.8668187822745</v>
+          <t>888 SWIFT BVLD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RICHLAND</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>888 SWIFT BVLD</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>RICHLAND</t>
+          <t>99352</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
           <t>509-942-2619</t>
         </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>99352</t>
-        </is>
-      </c>
-      <c r="N9">
-        <v>46.281615</v>
-      </c>
-      <c r="O9">
-        <v>-119.28156</v>
       </c>
     </row>
     <row r="10">
@@ -948,60 +832,48 @@
           <t>PROVIDENCE ST MARY MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C10">
-        <v>16.6870167305244</v>
-      </c>
-      <c r="D10">
-        <v>70.051282051282</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>-24.0815919073605</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G10">
-        <v>-24.0815919073605</v>
+          <t>401 W POPLAR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>WALLA WALLA</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>401 W POPLAR</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WALLA WALLA</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
           <t>509-522-5722</t>
         </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="N10">
-        <v>46.062933</v>
-      </c>
-      <c r="O10">
-        <v>-118.34311</v>
       </c>
     </row>
     <row r="11">
@@ -1015,60 +887,48 @@
           <t>ST CHRISTOPHER'S HOSP FOR CHILDREN/ TOWER HEALTH SYSTEM</t>
         </is>
       </c>
-      <c r="C11">
-        <v>10.3951434124155</v>
-      </c>
-      <c r="D11">
-        <v>101.629629629629</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>-18.8442768411712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>-18.8442768411712</v>
+          <t>160 EAST ERIE AVENUE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PHILADELPHIA</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>160 EAST ERIE AVENUE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PHILADELPHIA</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
           <t>215-427-5000 x267</t>
         </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>19134</t>
-        </is>
-      </c>
-      <c r="N11">
-        <v>39.989604</v>
-      </c>
-      <c r="O11">
-        <v>-75.10909100000001</v>
       </c>
     </row>
     <row r="12">
@@ -1082,55 +942,43 @@
           <t>SAINT MARYS HOSPITAL</t>
         </is>
       </c>
-      <c r="C12">
-        <v>8.25074439797784</v>
-      </c>
-      <c r="D12">
-        <v>95.93333333333329</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>-36.6226546212647</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>-36.6226546212647</v>
+          <t>56 FRANKLIN ST</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>WATERBURY</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>56 FRANKLIN ST</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WATERBURY</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+          <t>06706</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>203-574-6060</t>
         </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>06706</t>
-        </is>
-      </c>
-      <c r="N12">
-        <v>41.552275</v>
-      </c>
-      <c r="O12">
-        <v>-73.03603</v>
       </c>
     </row>
     <row r="13">
@@ -1144,60 +992,48 @@
           <t>RILEY HOSPITAL FOR CHILDREN</t>
         </is>
       </c>
-      <c r="C13">
-        <v>5.58245527449911</v>
-      </c>
-      <c r="D13">
-        <v>1232.15384615384</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>-15.7572730677987</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G13">
-        <v>-15.7572730677987</v>
+          <t>705 RILEY HOSPITAL DRIVE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>INDIANAPOLIS</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>705 RILEY HOSPITAL DRIVE</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS</t>
+          <t>46202</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HEATHER VAUGHT</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>HEATHER VAUGHT</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
           <t>317-948-9627</t>
         </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>46202</t>
-        </is>
-      </c>
-      <c r="N13">
-        <v>39.777276</v>
-      </c>
-      <c r="O13">
-        <v>-86.18141</v>
       </c>
     </row>
     <row r="14">
@@ -1211,60 +1047,48 @@
           <t>ST JOSEPH HOSPITAL JOLIET</t>
         </is>
       </c>
-      <c r="C14">
-        <v>13.2301658733482</v>
-      </c>
-      <c r="D14">
-        <v>87.375</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>-42.5464949928469</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>-42.5464949928469</v>
+          <t>333 N MADISON ST</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>JOLIET</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>333 N MADISON ST</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>JOLIET</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>JANIKA BAKI-ALLING</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>JANIKA BAKI-ALLING</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
           <t>815-725-7133</t>
         </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>60435</t>
-        </is>
-      </c>
-      <c r="N14">
-        <v>41.527927</v>
-      </c>
-      <c r="O14">
-        <v>-88.136002</v>
       </c>
     </row>
     <row r="15">
@@ -1278,60 +1102,48 @@
           <t>ST VINCENTS HOSPITAL BIRMINGHAM</t>
         </is>
       </c>
-      <c r="C15">
-        <v>12.7396665417757</v>
-      </c>
-      <c r="D15">
-        <v>140.926829268292</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>-20.0530748817353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G15">
-        <v>-20.0530748817353</v>
+          <t>810 ST VINCENT DRIVE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>BIRMINGHAM</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>810 ST VINCENT DRIVE</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BIRMINGHAM</t>
+          <t>35205</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>KELLEY HALL</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>KELLEY HALL</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
           <t>205-939-7057</t>
         </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>35205</t>
-        </is>
-      </c>
-      <c r="N15">
-        <v>33.507536</v>
-      </c>
-      <c r="O15">
-        <v>-86.78923</v>
       </c>
     </row>
     <row r="16">
@@ -1345,60 +1157,48 @@
           <t>LOUIS STOKES VA MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C16">
-        <v>9.62129512490486</v>
-      </c>
-      <c r="D16">
-        <v>110.28125</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Low penetration</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>-19.4987563363873</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Low penetration</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>-19.4987563363873</v>
+          <t>10701 EAST BOULEVARD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CLEVELAND</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>10701 EAST BOULEVARD</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLEVELAND</t>
+          <t>44106</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>LABORATORY 113W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LABORATORY 113W</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
           <t>216-791-3800</t>
         </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>44106</t>
-        </is>
-      </c>
-      <c r="N16">
-        <v>41.512491</v>
-      </c>
-      <c r="O16">
-        <v>-81.61351999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1412,60 +1212,48 @@
           <t>FREDERICK FERRIS THOMPSON HOSPITAL</t>
         </is>
       </c>
-      <c r="C17">
-        <v>46.4419509900482</v>
-      </c>
-      <c r="D17">
-        <v>35.6071428571428</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>-43.7038387890945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>-43.7038387890945</v>
+          <t>350 PARRISH STREET</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CANANDAIGUA</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>350 PARRISH STREET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CANANDAIGUA</t>
+          <t>14424</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
           <t>585-396-6000</t>
         </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>14424</t>
-        </is>
-      </c>
-      <c r="N17">
-        <v>42.876373</v>
-      </c>
-      <c r="O17">
-        <v>-77.28874999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1479,60 +1267,48 @@
           <t>PIEDMONT ATHENS REGIONAL HOSPITAL</t>
         </is>
       </c>
-      <c r="C18">
-        <v>45.6494713016452</v>
-      </c>
-      <c r="D18">
-        <v>162.477272727272</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>-82.56166363593969</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>-82.56166363593969</v>
+          <t>1199 PRINCE AVE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ATHENS</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1199 PRINCE AVE</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ATHENS</t>
+          <t>30606</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
           <t>706-475-3803</t>
         </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>30606</t>
-        </is>
-      </c>
-      <c r="N18">
-        <v>33.962393</v>
-      </c>
-      <c r="O18">
-        <v>-83.39774</v>
       </c>
     </row>
     <row r="19">
@@ -1546,55 +1322,43 @@
           <t>CONCORD HOSPITAL</t>
         </is>
       </c>
-      <c r="C19">
-        <v>42.5627112178919</v>
-      </c>
-      <c r="D19">
-        <v>71.3030303030303</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>-47.3663158421039</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>-47.3663158421039</v>
+          <t>250 PLEASANT STREET</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CONCORD</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>250 PLEASANT STREET</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CONCORD</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+          <t>03301</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>603-225-2711 x4630</t>
         </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>03301</t>
-        </is>
-      </c>
-      <c r="N19">
-        <v>43.196422</v>
-      </c>
-      <c r="O19">
-        <v>-71.56281</v>
       </c>
     </row>
     <row r="20">
@@ -1608,55 +1372,43 @@
           <t>GREAT PLAINS HEALTH</t>
         </is>
       </c>
-      <c r="C20">
-        <v>28.0031610962456</v>
-      </c>
-      <c r="D20">
-        <v>55.8181818181818</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>-45.7271507951715</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>-45.7271507951715</v>
+          <t>601 W LEOTA STREET</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NORTH PLATTE</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>601 W LEOTA STREET</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NORTH PLATTE</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NE</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+          <t>69101</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>308-534-9310</t>
         </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>69101</t>
-        </is>
-      </c>
-      <c r="N20">
-        <v>41.120741</v>
-      </c>
-      <c r="O20">
-        <v>-100.77091</v>
       </c>
     </row>
     <row r="21">
@@ -1670,60 +1422,48 @@
           <t>DENVER HEALTH MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C21">
-        <v>35.8015566840924</v>
-      </c>
-      <c r="D21">
-        <v>108.074074074074</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>-18.9766665673332</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>-18.9766665673332</v>
+          <t>777 BANNOCK STREET MC-0224</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DENVER</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>777 BANNOCK STREET MC-0224</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DENVER</t>
+          <t>80204</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>MOLLY GREVEL</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>MOLLY GREVEL</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
           <t>303-602-5251</t>
         </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>80204</t>
-        </is>
-      </c>
-      <c r="N21">
-        <v>39.727945</v>
-      </c>
-      <c r="O21">
-        <v>-104.99146</v>
       </c>
     </row>
     <row r="22">
@@ -1737,60 +1477,48 @@
           <t>BAY AREA HEALTH DISTRICT</t>
         </is>
       </c>
-      <c r="C22">
-        <v>50.4801217301217</v>
-      </c>
-      <c r="D22">
-        <v>46.4090909090909</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E22">
+        <v>-61.2144955925563</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>-61.2144955925563</v>
+          <t>1775 THOMPSON RD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>COOS BAY</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1775 THOMPSON RD</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COOS BAY</t>
+          <t>97420</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
           <t>541-269-8446</t>
         </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>97420</t>
-        </is>
-      </c>
-      <c r="N22">
-        <v>43.383449</v>
-      </c>
-      <c r="O22">
-        <v>-124.233</v>
       </c>
     </row>
     <row r="23">
@@ -1804,60 +1532,48 @@
           <t>SKY LAKES MEDICAL CENTER</t>
         </is>
       </c>
-      <c r="C23">
-        <v>32.0172627080521</v>
-      </c>
-      <c r="D23">
-        <v>25.7894736842105</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>-38.9285714285714</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G23">
-        <v>-38.9285714285714</v>
+          <t>2865 DAGGETT AVENUE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KLAMATH FALLS</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2865 DAGGETT AVENUE</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>KLAMATH FALLS</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
           <t>541-274-4529</t>
         </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>97601</t>
-        </is>
-      </c>
-      <c r="N23">
-        <v>42.252633</v>
-      </c>
-      <c r="O23">
-        <v>-121.78739</v>
       </c>
     </row>
     <row r="24">
@@ -1871,55 +1587,43 @@
           <t>PRISMA HEALTH TUOMEY HOSPITAL</t>
         </is>
       </c>
-      <c r="C24">
-        <v>27.1158538211505</v>
-      </c>
-      <c r="D24">
-        <v>48.8918918918918</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>-36.7521367521367</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>-36.7521367521367</v>
+          <t>129 N WASHINGTON ST</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SUMTER</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>129 N WASHINGTON ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SUMTER</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+          <t>29150</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>803-774-9183</t>
         </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>29150</t>
-        </is>
-      </c>
-      <c r="N24">
-        <v>33.923498</v>
-      </c>
-      <c r="O24">
-        <v>-80.34435999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1933,60 +1637,48 @@
           <t>ST JOSEPH HOSPITAL ELGIN</t>
         </is>
       </c>
-      <c r="C25">
-        <v>34.7222222222222</v>
-      </c>
-      <c r="D25">
-        <v>29.4285714285714</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>-56.3915857605178</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>-56.3915857605178</v>
+          <t>77 N AIRLITE ST</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ELGIN</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>77 N AIRLITE ST</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ELGIN</t>
+          <t>60123</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>FARAH ZAIDI</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>FARAH ZAIDI</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
           <t>847-695-3200</t>
         </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>60123</t>
-        </is>
-      </c>
-      <c r="N25">
-        <v>42.035345</v>
-      </c>
-      <c r="O25">
-        <v>-88.325858</v>
       </c>
     </row>
     <row r="26">
@@ -2000,60 +1692,48 @@
           <t>MERIT HEALTH WESLEY</t>
         </is>
       </c>
-      <c r="C26">
-        <v>25.5585434173669</v>
-      </c>
-      <c r="D26">
-        <v>44.6888888888888</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>-44.9527598209845</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>-44.9527598209845</v>
+          <t>5001 HARDY STREET</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HATTIESBURG</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5001 HARDY STREET</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>HATTIESBURG</t>
+          <t>39402</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LEE BYRD</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LEE BYRD</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
           <t>601-268-8139</t>
         </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>39402</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>31.32304</v>
-      </c>
-      <c r="O26">
-        <v>-89.36708</v>
       </c>
     </row>
     <row r="27">
@@ -2067,60 +1747,48 @@
           <t>ADVENTIST HEALTH ST HELENA</t>
         </is>
       </c>
-      <c r="C27">
-        <v>50.0302431606497</v>
-      </c>
-      <c r="D27">
-        <v>126.65625</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Moderate penetration</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>-34.6437481152507</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Moderate penetration</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>-34.6437481152507</v>
+          <t>10 WOODLAND ROAD</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SAINT HELENA</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10 WOODLAND ROAD</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SAINT HELENA</t>
+          <t>94574</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>BB LEAD-LISA LAMBERT</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>BB LEAD-LISA LAMBERT</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
           <t>707-463-7301</t>
         </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>94574</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>38.541668</v>
-      </c>
-      <c r="O27">
-        <v>-122.47547</v>
       </c>
     </row>
     <row r="28">
@@ -2134,60 +1802,48 @@
           <t>ADVENTIST HEALTH SIMI VALLEY</t>
         </is>
       </c>
-      <c r="C28">
-        <v>52.9749103942652</v>
-      </c>
-      <c r="D28">
-        <v>74.67441860465109</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>High penetration</t>
+        </is>
+      </c>
+      <c r="E28">
+        <v>-77.2345063843039</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>High penetration</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>-77.2345063843039</v>
+          <t>2975 SYCAMORE DRIVE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SIMI VALLEY</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2975 SYCAMORE DRIVE</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SIMI VALLEY</t>
+          <t>93065</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>HOLLY TEICH</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>HOLLY TEICH</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
           <t>┬Ç805-955-6350</t>
         </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>93065</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>34.288856</v>
-      </c>
-      <c r="O28">
-        <v>-118.74394</v>
       </c>
     </row>
     <row r="29">
@@ -2201,60 +1857,48 @@
           <t>RICE MEMORIAL HOSPITAL</t>
         </is>
       </c>
-      <c r="C29">
-        <v>75.21154133223089</v>
-      </c>
-      <c r="D29">
-        <v>31.9459459459459</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>High penetration</t>
+        </is>
+      </c>
+      <c r="E29">
+        <v>-60.5102173630092</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>High penetration</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>-60.5102173630092</v>
+          <t>301 BECKER AVE SW</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>WILLMAR</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>301 BECKER AVE SW</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>WILLMAR</t>
+          <t>56201</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>BLOOD BANK</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
           <t>320-231-4512</t>
         </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>56201</t>
-        </is>
-      </c>
-      <c r="N29">
-        <v>45.120537</v>
-      </c>
-      <c r="O29">
-        <v>-95.04631999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2268,30 +1912,18 @@
           <t>PIEDMONT MEDICAL CENTER - FORT MILL</t>
         </is>
       </c>
-      <c r="C30">
-        <v>55.9075448361162</v>
-      </c>
-      <c r="D30">
-        <v>28.5142857142857</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>High penetration</t>
         </is>
       </c>
-      <c r="G30">
+      <c r="E30">
         <v>-52.9058116232464</v>
-      </c>
-      <c r="N30">
-        <v>35.021546</v>
-      </c>
-      <c r="O30">
-        <v>-80.928434</v>
       </c>
     </row>
     <row r="31">
@@ -2305,60 +1937,48 @@
           <t>MEMORIAL HOSPITAL-BILOXI</t>
         </is>
       </c>
-      <c r="C31">
-        <v>74.4293272864701</v>
-      </c>
-      <c r="D31">
-        <v>30.2758620689655</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>High penetration</t>
+        </is>
+      </c>
+      <c r="E31">
+        <v>-68.8577936869508</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>High penetration</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>-68.8577936869508</v>
+          <t>150 REYNOIR ST</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>BILOXI</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>150 REYNOIR ST</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BILOXI</t>
+          <t>39530</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SOPHIA BARLOW</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>SOPHIA BARLOW</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
           <t>228-436-1269</t>
         </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>39530</t>
-        </is>
-      </c>
-      <c r="N31">
-        <v>30.396057</v>
-      </c>
-      <c r="O31">
-        <v>-88.89045</v>
       </c>
     </row>
   </sheetData>

--- a/hosp3down.xlsx
+++ b/hosp3down.xlsx
@@ -455,11 +455,6 @@
           <t>13676</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>315-265-3300</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -657,12 +652,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>48503</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>810-262-9000</t>
+          <t>48502</t>
         </is>
       </c>
     </row>
@@ -692,7 +682,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>416 CONNABLE AVE</t>
+          <t>416 CONNABLE AVENUE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -708,11 +698,6 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>49770</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>231-487-4165</t>
         </is>
       </c>
     </row>
@@ -760,11 +745,6 @@
           <t>42003</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>270-444-2142</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -792,32 +772,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>888 SWIFT BVLD</t>
+          <t>PO BOX 31263</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>RICHLAND</t>
+          <t>SALT LAKE CITY</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>99352</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>509-942-2619</t>
+          <t>84131</t>
         </is>
       </c>
     </row>
@@ -847,7 +817,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>401 W POPLAR</t>
+          <t>PO BOX 1477</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -863,16 +833,6 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>99362</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>509-522-5722</t>
         </is>
       </c>
     </row>
@@ -902,7 +862,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>160 EAST ERIE AVENUE</t>
+          <t>PO BOX 26968</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -918,16 +878,6 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>19134</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>215-427-5000 x267</t>
         </is>
       </c>
     </row>
@@ -957,27 +907,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56 FRANKLIN ST</t>
+          <t>TRINITY HEALTH</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>WATERBURY</t>
+          <t>TROY</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>06706</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>203-574-6060</t>
+          <t>48007-7007</t>
         </is>
       </c>
     </row>
@@ -1007,7 +952,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>705 RILEY HOSPITAL DRIVE</t>
+          <t>350 WEST 11TH ROOM 5006</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1023,16 +968,6 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>46202</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>HEATHER VAUGHT</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>317-948-9627</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1052,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>810 ST VINCENT DRIVE</t>
+          <t>PO BOX 12407</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1132,17 +1067,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35205</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>KELLEY HALL</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>205-939-7057</t>
+          <t>35202-2407</t>
         </is>
       </c>
     </row>
@@ -1172,32 +1097,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10701 EAST BOULEVARD</t>
+          <t>DEPT OF VETERAN AFFAIRS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CLEVELAND</t>
+          <t>AUSTIN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>44106</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>LABORATORY 113W</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>216-791-3800</t>
+          <t>78714</t>
         </is>
       </c>
     </row>
@@ -1245,16 +1160,6 @@
           <t>14424</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>585-396-6000</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1282,7 +1187,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1199 PRINCE AVE</t>
+          <t>1199 PRINCE AVENUE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1298,16 +1203,6 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>BLOOD BANK</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>706-475-3803</t>
         </is>
       </c>
     </row>
@@ -1355,11 +1250,6 @@
           <t>03301</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>603-225-2711 x4630</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1620,11 +1510,6 @@
           <t>29150</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>803-774-9183</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1817,12 +1702,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2975 SYCAMORE DRIVE</t>
+          <t>PO BOX 619085</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SIMI VALLEY</t>
+          <t>ROSEVILLE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1832,17 +1717,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>93065</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>HOLLY TEICH</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>┬Ç805-955-6350</t>
+          <t>95661</t>
         </is>
       </c>
     </row>
@@ -1925,6 +1800,31 @@
       <c r="E30">
         <v>-52.9058116232464</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1000 WELLNESS WAY</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>FORT MILL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>29715</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CHARLES JENKINS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1952,7 +1852,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>150 REYNOIR ST</t>
+          <t>PO DRAWER 128</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1968,16 +1868,6 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>39530</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>SOPHIA BARLOW</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>228-436-1269</t>
         </is>
       </c>
     </row>

--- a/hosp3down.xlsx
+++ b/hosp3down.xlsx
@@ -455,6 +455,11 @@
           <t>13676</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>315-265-3300</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,7 +597,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>420 N. CENTER STREET</t>
+          <t>ALEXANDER CAMPUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -603,11 +608,6 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>NC</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>28601</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>48502</t>
+          <t>48503</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>810-262-9000</t>
         </is>
       </c>
     </row>
@@ -682,7 +687,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>416 CONNABLE AVENUE</t>
+          <t>416 CONNABLE AVE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -698,6 +703,11 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>49770</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>231-487-4165</t>
         </is>
       </c>
     </row>
@@ -745,6 +755,11 @@
           <t>42003</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>270-444-2142</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -772,22 +787,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PO BOX 31263</t>
+          <t>888 SWIFT BVLD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SALT LAKE CITY</t>
+          <t>RICHLAND</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>84131</t>
+          <t>99352</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>509-942-2619</t>
         </is>
       </c>
     </row>
@@ -817,7 +842,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PO BOX 1477</t>
+          <t>401 W POPLAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -833,6 +858,16 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>99362</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>509-522-5722</t>
         </is>
       </c>
     </row>
@@ -862,7 +897,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PO BOX 26968</t>
+          <t>160 EAST ERIE AVENUE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -878,6 +913,16 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>19134</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>215-427-5000 x267</t>
         </is>
       </c>
     </row>
@@ -907,22 +952,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRINITY HEALTH</t>
+          <t>56 FRANKLIN ST</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TROY</t>
+          <t>WATERBURY</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>48007-7007</t>
+          <t>06706</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>203-574-6060</t>
         </is>
       </c>
     </row>
@@ -952,7 +1002,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>350 WEST 11TH ROOM 5006</t>
+          <t>705 RILEY HOSPITAL DRIVE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -968,6 +1018,16 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>46202</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>HEATHER VAUGHT</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>317-948-9627</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1112,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PO BOX 12407</t>
+          <t>810 ST VINCENT DRIVE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1067,7 +1127,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35202-2407</t>
+          <t>35205</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>KELLEY HALL</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>205-939-7057</t>
         </is>
       </c>
     </row>
@@ -1097,22 +1167,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DEPT OF VETERAN AFFAIRS</t>
+          <t>10701 EAST BOULEVARD</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AUSTIN</t>
+          <t>CLEVELAND</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>78714</t>
+          <t>44106</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>LABORATORY 113W</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>216-791-3800</t>
         </is>
       </c>
     </row>
@@ -1160,6 +1240,16 @@
           <t>14424</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>585-396-6000</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1187,7 +1277,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1199 PRINCE AVENUE</t>
+          <t>1199 PRINCE AVE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1203,6 +1293,16 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>30606</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BLOOD BANK</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>706-475-3803</t>
         </is>
       </c>
     </row>
@@ -1250,6 +1350,11 @@
           <t>03301</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>603-225-2711 x4630</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1510,6 +1615,11 @@
           <t>29150</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>803-774-9183</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1702,12 +1812,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PO BOX 619085</t>
+          <t>2975 SYCAMORE DRIVE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ROSEVILLE</t>
+          <t>SIMI VALLEY</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1717,7 +1827,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>95661</t>
+          <t>93065</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>HOLLY TEICH</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>┬Ç805-955-6350</t>
         </is>
       </c>
     </row>
@@ -1800,31 +1920,6 @@
       <c r="E30">
         <v>-52.9058116232464</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1000 WELLNESS WAY</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>FORT MILL</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>29715</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>CHARLES JENKINS</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1852,7 +1947,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PO DRAWER 128</t>
+          <t>150 REYNOIR ST</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1868,6 +1963,16 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>39530</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SOPHIA BARLOW</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>228-436-1269</t>
         </is>
       </c>
     </row>

--- a/hosp3down.xlsx
+++ b/hosp3down.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ALEXANDER CAMPUS</t>
+          <t>420 N. CENTER STREET</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -608,6 +608,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>NC</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>28601</t>
         </is>
       </c>
     </row>
@@ -1919,6 +1924,31 @@
       </c>
       <c r="E30">
         <v>-52.9058116232464</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1000 WELLNESS WAY</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>FORT MILL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>29715</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CHARLES JENKINS</t>
+        </is>
       </c>
     </row>
     <row r="31">
